--- a/Phase6.2/quantized (Cleaned)/load_35.xlsx
+++ b/Phase6.2/quantized (Cleaned)/load_35.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8720"/>
+    <workbookView windowWidth="18350" windowHeight="8720"/>
   </bookViews>
   <sheets>
     <sheet name="Timestamp logs" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +490,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,118 +523,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -703,6 +696,9407 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Sensing Unit Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$A$1:$A$498</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="498"/>
+                <c:pt idx="0">
+                  <c:v>25.6212</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.6466</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.4296</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.8639</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26.2972</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18.2454</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.4355</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28.103</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22.5511</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.2132</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18.7901</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>29.4192</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25.7785</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.2354</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>21.2969</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.5817</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>21.5818</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>151.3089</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24.9729</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21.6212</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>24.4839</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21.129</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>25.8566</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>25.4797</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>16.3422</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>20.1674</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>30.8462</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>29.3264</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>19.1647</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>34.3469</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>22.8362</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>20.2563</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>41.5245</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>31.1203</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34.4307</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>38.2972</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>18.4534</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>28.2734</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>28.0851</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>32.5961</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>32.5234</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>23.9391</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>37.0156</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>31.4898</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>24.5377</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>34.5875</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>19.029</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>30.9677</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>29.683</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>19.925</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>30.0192</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>35.4211</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>21.6885</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>23.8672</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>41.4438</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>29.2541</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>44.1794</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>44.3645</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18.9286</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>36.5543</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>22.6947</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>36.0397</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>35.2235</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>16.4123</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>48.6272</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>34.7429</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>24.1405</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>37.8866</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>38.7096</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>25.9311</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>30.402</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>29.0638</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>45.0011</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>25.8902</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>36.4434</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>18.0435</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>15.016</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>26.9589</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>25.6909</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>29.758</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>16.3676</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>22.3</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>27.0294</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>27.2296</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>30.0527</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>21.5135</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>22.8403</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>16.7835</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>17.9362</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>18.5063</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>19.4391</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>39.1285</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>19.5747</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>27.0051</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>29.7835</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>16.0539</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>32.1272</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>39.4842</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>20.4429</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>25.2357</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>24.9792</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>31.8061</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>29.8995</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>31.4495</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>25.8162</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>27.7423</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>33.271</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45.5114</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>21.2462</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>35.5029</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>18.8223</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>13.8463</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>26.446</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>12.6388</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>14.9418</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>30.5688</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>19.3918</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>11.5374</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>11.0479</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>10.4971</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>11.7943</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>11.3329</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>13.0493</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>14.9561</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>10.6806</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>15.4929</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>14.0482</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>14.0695</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>11.9891</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>17.6732</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>12.632</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>11.8653</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>13.5522</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>21.7826</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>10.9496</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>10.4133</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>13.122</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>10.431</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>10.3416</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>22.4824</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>20.728</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>17.0464</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>18.9123</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>26.4389</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>28.3881</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>10.5315</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>10.4843</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>14.3322</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>13.2368</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>12.3234</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>10.7309</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>19.2473</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>10.898</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>9.7058</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>25.0604</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>13.1233</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>11.1999</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>10.5063</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>19.2739</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>13.944</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>18.7365</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>12.9168</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>11.5224</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>10.7804</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>14.1936</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>25.6699</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>9.1501</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>12.8209</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>11.1533</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>29.5917</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>26.4928</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>10.1616</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>11.5107</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>13.0034</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>15.22</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>11.3414</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>9.2686</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>9.8208</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>12.9292</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>12.5065</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>10.314</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>16.3347</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>12.5434</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>20.2471</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>22.2888</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>11.1777</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>20.6202</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>16.679</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>11.8414</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>15.2082</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>20.7149</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>25.5534</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>20.5897</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>10.9763</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>12.1077</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>12.4041</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>9.767</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>20.9641</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>14.3988</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>13.1769</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>12.3672</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>11.6924</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>13.954</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>12.9646</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>20.4214</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>20.9035</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>17.8224</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>11.3991</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>22.9311</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>15.4679</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>17.6767</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>15.1543</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>10.1596</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>16.6002</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>21.7156</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>17.0775</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>18.4996</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>11.5285</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>14.9674</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>24.2534</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>19.265</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>15.7712</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>12.657</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>15.5475</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>12.4565</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>19.599</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>13.006</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>17.2206</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>22.9101</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>21.0942</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>10.7474</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>11.9372</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>20.0223</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>11.9767</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>27.2858</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>16.9192</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>13.4209</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>10.6564</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>10.7798</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>10.424</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>10.6646</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>22.8034</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>12.0881</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>12.0547</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>15.7464</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>13.0605</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>17.6875</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>11.8241</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>17.8527</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>19.0382</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>20.836</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>19.9307</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>10.6128</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>16.4006</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>18.65</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>13.9259</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>24.1989</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>13.3206</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>18.4671</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>14.8969</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>12.8183</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>10.8561</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>17.8825</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>16.3205</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>13.731</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>11.2197</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>16.0638</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>17.0605</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>12.814</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>15.1369</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>32.5549</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>17.8004</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>17.2258</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>11.8121</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>21.5285</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>18.2635</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>10.6651</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>21.2433</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>10.3624</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>11.2115</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>10.4788</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>20.0677</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>12.8322</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>11.278</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>12.7838</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>11.5361</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>18.6469</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>16.0756</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>18.3658</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>10.7534</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>18.3595</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>11.5916</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>17.4763</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>16.041</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>23.5967</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>23.5394</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>14.8769</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>16.1953</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>17.0677</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>14.0629</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>20.2036</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>11.5428</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>15.3323</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>14.8247</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>11.2725</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>16.8337</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>12.3627</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>17.9489</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>17.873</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>22.8699</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>12.1397</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>10.3133</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>20.3865</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>15.5733</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>9.7428</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>14.3901</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>12.2127</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>20.0917</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>10.6388</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>19.3299</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>17.7997</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>9.8636</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>21.2947</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>12.2987</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>18.3717</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>10.1521</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>10.8278</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>17.9631</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>20.5101</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>11.9267</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>10.2396</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>9.9949</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>25.3821</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>15.5498</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>21.2424</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>15.4687</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>10.9074</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>18.66</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>10.1219</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>12.6917</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>20.2073</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>10.3903</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>10.8803</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>10.6542</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>20.5087</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>18.7662</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>17.7638</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>11.0318</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>14.2883</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>16.6813</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>11.3139</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>13.1043</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>19.4903</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>16.765</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>20.6339</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>11.0292</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>10.8007</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>17.9967</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>11.4151</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>23.0024</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>11.1521</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>13.1907</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>11.7268</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>13.0431</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>19.9837</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>126.6529</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>20.3156</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>12.9376</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>13.0939</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>12.1466</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>9.9071</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>11.9473</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>20.9018</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>21.2626</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>16.4273</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>17.1007</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>21.5984</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>21.8241</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>21.1873</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>25.5057</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>16.3531</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>11.8178</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>19.431</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>20.7417</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>19.0029</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>20.3819</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>20.4278</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>19.9516</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>13.8503</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>22.8759</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>20.4738</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>14.4625</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>10.7774</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>11.1231</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>10.8352</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>10.7948</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>16.9249</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>17.7764</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>27.4541</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>10.9458</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>15.8367</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>12.6486</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>20.9699</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>16.9153</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>11.3757</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>11.4461</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>14.952</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>12.4887</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>19.3514</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>13.8257</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>14.4997</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>17.396</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>13.1051</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>15.2879</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>23.901</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>14.3283</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>10.3494</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>12.3151</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>9.1795</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>9.697</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>18.0739</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>11.3706</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>22.6251</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>18.1977</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>10.758</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>15.0061</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>24.2359</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>9.7887</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>15.2551</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>18.6352</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>17.1439</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>20.4417</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>15.0378</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>10.9191</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>13.0261</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>22.2062</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>22.5435</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>13.4724</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>10.4116</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>19.3425</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>17.4111</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>13.346</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>17.211</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>16.3679</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>14.7392</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>10.1961</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>117.0114</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>25.6302</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>12.6535</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>13.8696</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>11.4579</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>17.859</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>10.3564</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>11.3517</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>18.3014</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>10.177</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>11.7179</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>11.2366</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>21.5646</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>20.9262</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>12.6639</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>23.5544</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>23.9288</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>20.3417</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>14.0424</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>11.1793</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>11.1284</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>13.0242</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>13.5408</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>21.1513</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>11.9203</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>10.7363</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>11.9441</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>15.0096</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>11.784</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>10.3396</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>10.4855</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>19.6591</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>17.2084</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>12.4243</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>21.3649</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>11.1274</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>10.2078</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>15.3012</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>10.3194</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>12.2732</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>26.2184</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>95.1349</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>11.5021</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>14.4815</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>10.9119</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>11.7214</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>13.5642</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>20.75</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>14.1343</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>17.8046</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>14.5803</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>12.0346</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="112649023"/>
+        <c:axId val="783397726"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="112649023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="783397726"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="783397726"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="112649023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Queue Lifetime: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$B$1:$B$498</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="498"/>
+                <c:pt idx="0">
+                  <c:v>0.081756</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.280388</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>363.171915</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>427.495157</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>571.212029</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>739.635678</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>758.905041</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>816.379225</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>874.543435</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1037.537268</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1146.501647</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1313.50859</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1893.466456</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2041.713664</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2206.620282</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2304.646824</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2545.49043</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2523.607728</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2843.485596</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3026.704679</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3187.072619</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3340.302442</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3539.184977</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3592.776835</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3640.838493</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4126.486915</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4429.314277</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4428.468384</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4464.087124</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4489.605376</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4995.736493</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5046.205177</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5118.196706</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5259.367059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>5440.92253</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5581.444483</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>5828.455213</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5898.079322</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5985.034582</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6347.604173</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6484.165023</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6465.139925</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>6490.168741</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>6341.827254</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>6440.99878</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>6121.184989</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>6138.460072</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6011.341144</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>6081.567698</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5973.485471</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5893.984629</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5571.932986</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5778.550145</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5722.709547</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5576.551523</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5874.764978</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5494.799252</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5247.194214</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5408.44669</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5511.355348</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5662.07043</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5284.765615</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5448.651233</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5249.359048</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5400.730955</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5284.059003</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5295.678954</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5007.626263</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4918.847327</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4985.297375</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4922.373939</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4806.389252</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4691.941715</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>4659.10736</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4805.070394</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4648.766492</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4717.498332</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5130.922846</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>4997.796403</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5200.065504</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4922.412513</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5155.868656</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5150.407776</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5329.536199</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5196.423611</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5250.856421</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4893.002727</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5180.820839</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5305.345693</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5248.4712</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5033.841564</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4924.792814</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4888.259104</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4845.973159</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4862.992029</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4659.488693</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4987.498049</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4890.855338</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4930.052122</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4665.79345</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4998.421063</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4881.430585</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4907.81374</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5181.073343</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4962.61983</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5057.345222</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4959.521386</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4666.47554</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4611.848041</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4450.269627</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4568.650642</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4543.770646</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4587.027824</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4356.476182</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4405.978746</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4624.396694</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4621.057582</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4524.038522</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4727.682924</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4672.708435</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4754.528425</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4671.51361</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4796.899618</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4805.235315</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4717.75185</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4633.644437</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4668.291188</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4677.759238</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4725.492254</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4839.537617</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4438.326859</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4510.387236</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4651.057638</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4485.52884</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4177.511831</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4206.542316</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4450.408071</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4550.299797</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4583.432845</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4682.57211</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4582.088089</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4478.203287</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4890.400459</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4625.76092</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4591.067396</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4412.959089</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4565.29166</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4490.672715</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4277.311409</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4276.860708</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>4511.02587</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>4488.660906</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>4260.809965</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>4421.510514</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4445.689895</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>4460.388964</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4466.124777</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>4438.001695</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>4429.838509</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>4583.271206</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>4487.196911</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>4524.717424</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>4515.139008</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>4568.232253</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>4638.144008</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>4484.274149</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4372.438962</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4274.643643</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4406.643297</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4110.914281</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4182.6502</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4141.255628</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3929.714868</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4111.048598</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4047.972098</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3961.939971</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4141.305192</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4082.231522</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4433.556013</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4384.868649</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4036.377036</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4058.252203</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>4281.099318</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4125.493924</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4096.098694</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4111.432448</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4076.456311</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>3995.694917</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4244.245274</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>3926.372887</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4036.916872</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4017.965758</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4129.086598</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4158.988926</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4011.493979</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4210.769166</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>4150.104274</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>4050.113386</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>3868.268429</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>3935.689232</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>4182.397551</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>4160.154381</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>3927.752204</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>3837.715372</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3844.537826</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>4062.874027</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>3766.502753</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>3779.274211</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>3459.496044</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3643.166443</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>3625.774947</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>3653.187061</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3372.468053</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>3674.327919</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>3573.08617</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>3546.996962</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>3286.280331</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>3252.953079</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>3257.921013</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>3305.822583</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>3386.3245</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>3218.595758</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>3067.015766</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>3170.424954</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>3046.480386</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>3020.65525</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>2926.181965</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>3110.919377</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>3056.106733</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>3039.312702</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>2943.649677</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>2943.031109</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>2930.856705</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>2887.773249</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>2955.064036</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>2907.549671</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>2914.343579</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>2970.445764</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>2965.672387</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>3075.660223</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>3128.24793</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>3102.236202</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>3137.613101</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>3011.746888</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>2988.985822</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>3130.008532</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>3215.346128</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>3253.394252</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3022.123521</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>3166.917602</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>3095.856348</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>3085.585464</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>2941.560631</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>2894.701916</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>3201.135507</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>3059.180982</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>3065.945196</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>3022.380546</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>3082.737892</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>2991.207056</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>3102.914342</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>3117.440661</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>3216.651164</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>3257.839588</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>3115.84305</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>3098.902257</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>3136.247089</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>3347.6273</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>3427.754383</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>3230.267402</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>3215.99688</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>3249.617432</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>3541.561692</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>3467.200898</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>3474.558235</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>3386.173821</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>3405.650839</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>3295.678438</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>3499.283448</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>3406.646708</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>3379.062895</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>3339.887942</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>3359.010222</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>3567.304459</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>3338.314553</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>3436.455314</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>3461.333736</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>3397.013449</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>3421.117453</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>3602.771313</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>3656.122242</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>3503.245982</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>3412.174469</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>3646.98497</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>3629.171725</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>3853.43485</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>3758.892781</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>3424.07455</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>3402.27472</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>3562.763814</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>3578.277326</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>3536.050098</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>3280.365349</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>3162.634967</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>3478.187907</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>3475.637677</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>3432.737887</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>3483.714209</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>3442.18703</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>3554.02475</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>3437.562708</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>3676.358739</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>3647.303077</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>3403.331898</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>3375.638252</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>3428.488427</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>3551.21585</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>3644.262624</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>3566.432555</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>3283.740679</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>3379.034694</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>3583.93943</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>3619.014386</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>3271.902607</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>3423.49373</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>3285.62416</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>3412.672121</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>3487.798148</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>3495.526468</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>3367.564242</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>3372.737665</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>3349.073411</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>3493.106128</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>3524.055872</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>3156.52087</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>3246.786275</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>3575.49486</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>3637.382772</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>3521.86059</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>3408.58585</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>3387.036206</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>3369.830092</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>3531.101653</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>3551.063442</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>3568.909127</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>3726.715544</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>3624.672174</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>3571.461505</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>3534.963808</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>3682.509221</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>3670.71461</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>3414.73114</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>3580.542331</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>3612.083797</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>3733.929928</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>3642.098362</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>3559.693777</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>3499.991421</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>3529.523654</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>3722.28621</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>3644.419501</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>3565.268171</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>3645.021532</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>3688.605006</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>3788.228946</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>3691.585284</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>3458.907962</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>3372.552982</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>3694.52677</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>3678.756108</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>3744.566926</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>3545.089289</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>3414.763572</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>3798.905966</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>3784.141328</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>3673.67006</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>3514.769747</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>3819.524172</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>3789.162069</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>3697.534693</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>3648.328504</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>3710.573682</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>3652.616689</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>3598.601242</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>3514.095131</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>3607.853325</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>3600.224885</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>3531.033347</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>3705.032435</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>3456.344248</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>3450.860986</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>3776.72293</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>3576.166795</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>3507.097279</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>3316.448144</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>3543.065239</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>3528.795671</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>3625.801077</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>3314.656368</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>3271.729517</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>3526.856541</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>3620.409658</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>3560.424654</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>3356.960428</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>3366.315254</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>3305.59098</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>3538.437493</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>3290.22438</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>3388.500242</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>3431.887313</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>3425.269004</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>3651.905575</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>3571.255587</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>3581.115832</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>3489.73531</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>3656.493047</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>3574.769326</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>3543.487433</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>3542.388499</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>3650.658094</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>3754.469931</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>3540.946515</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>3555.171379</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>3737.281048</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>3744.295027</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>3456.256196</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>3523.969197</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>3420.580612</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>3849.378614</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>3903.671293</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>3646.254315</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>3642.957646</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>3659.521901</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>3884.373457</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>3737.240728</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>3848.782069</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>3666.72357</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>3658.953279</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>3520.163477</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>3553.157969</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>3600.574883</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>3443.427122</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>3339.784361</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>3368.9762</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>3645.532003</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>3412.666888</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>3310.44924</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>3347.745149</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>3563.166616</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>3576.053587</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>3603.160002</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>3562.788702</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>3434.481381</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>3404.957781</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>3496.609874</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>3611.670813</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>3583.733495</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>3622.9744</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>3333.750791</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>3293.564851</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>3400.146898</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>3389.501449</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>3414.648398</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>3226.30379</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>3137.569145</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>3210.403752</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>3265.286999</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>3264.173891</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>3302.052939</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>3229.644669</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>3353.36257</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>3601.802944</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>3547.380471</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>3533.639958</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>3362.163555</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>3412.764041</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>3607.163013</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>3466.749758</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>3636.311213</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>3705.686201</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>3584.835339</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>3771.440436</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>3916.544003</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>3960.011384</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>4006.757893</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>4028.40188</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>3914.160251</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>3819.847422</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>3979.84841</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>3999.363517</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>4118.041634</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>4208.576225</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>4339.603104</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>4250.523854</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>4329.717889</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>4387.970874</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>4694.44365</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>4640.682391</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="190797865"/>
+        <c:axId val="590434701"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="190797865"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="590434701"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="590434701"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="190797865"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Inference Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$C$1:$C$498</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="498"/>
+                <c:pt idx="0">
+                  <c:v>686.984069</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>488.882885</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>502.722806</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>489.342488</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>401.999159</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>397.617227</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>643.494782</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>399.520213</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1294.41795</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1298.151098</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>808.057579</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1055.605556</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>896.552643</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>591.469334</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>898.361293</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1005.180937</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1102.344977</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>790.396555</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1001.210564</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>597.941995</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>497.394608</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>901.972875</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1097.470932</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>919.180973</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>876.487114</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>493.854493</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>686.656563</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>730.758626</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>791.297085</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>899.602307</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>592.481327</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1089.531511</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>600.517913</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>603.012443</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>696.372409</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>898.766316</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>801.021118</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>898.444825</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>701.999427</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1103.967463</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>705.806137</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>893.403988</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>792.392248</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>402.980201</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>607.995143</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>442.42963</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>704.485539</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>503.99608</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>550.38742</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>987.493304</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>419.751986</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>497.817988</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>902.817768</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>511.24738</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>498.28844</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>500.304646</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>598.518086</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>786.520773</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>753.421114</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1002.256085</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>396.528418</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>703.780235</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>509.471096</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>590.388649</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>19903.859651</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>391.13742</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>619.027618</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>591.244762</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>599.724806</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>497.93388</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>792.735859</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>879.967695</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>650.324533</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1196.464785</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1007.028214</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>703.948078</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>819.951861</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>699.35677</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>587.340251</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>763.413686</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>801.013356</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>707.517703</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>598.984551</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>615.644553</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>486.062287</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>608.986176</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>598.861536</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>400.669185</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>401.546806</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>408.377062</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>495.935773</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>492.662833</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>818.614352</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>599.291823</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>602.869591</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>452.336304</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>648.400321</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>993.606134</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>697.882089</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>599.101519</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>698.453</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>805.750114</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>801.266048</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>603.881651</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>396.86066</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>594.254672</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>394.949186</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>595.010639</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>595.066136</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>702.160867</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>497.392693</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>701.628172</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>901.676509</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>500.160813</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>875.791166</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>591.43057</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>692.995611</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>493.274663</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>682.514221</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>688.12034</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>499.852769</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>309.776655</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>882.205002</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>582.998</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>399.075975</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>505.971568</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>301.02724</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>502.369668</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>599.901994</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>601.194177</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>429.307995</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>496.464679</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>602.950623</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>697.428188</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>811.79311</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>892.272107</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>682.609533</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>501.476856</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>891.280583</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>610.468776</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>604.769735</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>600.51883</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>389.719402</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>491.81319</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>499.825173</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>528.935259</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>604.84091</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>602.473814</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>417.35293</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>671.220838</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>491.491015</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>382.511973</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>802.181472</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>630.521177</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>511.777484</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>801.69748</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>393.648027</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>594.409056</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>699.92401</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>693.79417</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>504.394638</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>697.255806</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>317.506078</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>309.810222</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>600.058536</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>501.569248</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>409.291428</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>397.01853</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>594.446755</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>603.428556</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>504.688115</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>299.283953</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>603.729209</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>882.84458</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>894.966339</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>394.868345</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>568.319791</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>494.829244</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>416.748096</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>596.771513</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>404.703312</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>431.110349</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>808.315829</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>498.031401</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>868.715505</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>304.807359</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>595.398669</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>293.360961</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>791.938429</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>698.981808</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>496.952526</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>695.292855</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>528.294873</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>399.541887</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>498.294908</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>798.865469</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>497.142422</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>401.324726</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>499.126713</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>498.856229</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>501.788555</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>450.307253</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>396.564312</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>502.282525</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>696.461414</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>500.165907</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>412.501642</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>505.982632</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>676.902116</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>590.575791</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>513.49149</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>394.40251</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>393.933335</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>406.610326</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>615.199521</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>304.142363</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>794.878867</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>495.717342</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>595.509113</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>500.118867</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>505.303846</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>499.249956</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>589.698376</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>352.720714</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>398.70127</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>399.780066</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>476.475512</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>353.093369</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>390.115715</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>898.122008</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>396.007484</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>485.88777</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>545.163018</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>310.721957</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>871.393676</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>481.278049</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>516.400292</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>754.096375</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>416.193839</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>500.892081</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>503.594321</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>983.945557</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>499.260036</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>440.859396</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>396.210913</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>403.762839</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>407.671895</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>450.4092</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>399.817426</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>682.323893</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>490.794406</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>799.446283</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>395.400064</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>498.641046</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>403.658691</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>301.487395</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>501.8228</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>551.778612</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>1098.935814</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>496.245281</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>428.813607</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>411.245623</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>347.00823</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>999.575887</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>697.767447</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>584.496791</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>647.820166</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>900.837595</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>784.185066</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>797.58409</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>447.885553</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>694.516461</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>356.21427</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>696.852754</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>598.52422</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>410.356369</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>341.549169</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>406.911685</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>789.267588</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>498.082114</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>391.278134</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>513.724485</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>596.32057</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>417.665496</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>653.962867</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>602.043718</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>598.089912</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>494.155973</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>704.468099</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>544.356796</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>777.384755</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>849.215792</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>696.13933</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>396.894363</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>752.313279</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>583.014449</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>299.683139</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>498.641173</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>503.856188</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>801.456806</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>644.8136</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>497.821347</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>585.617162</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>705.935571</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>493.80188</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>449.601086</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>694.737986</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>685.286234</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>403.916404</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>508.546503</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>401.638982</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>500.827374</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>594.139096</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>596.573531</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>496.495292</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>496.307477</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>596.323667</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>503.715652</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>505.656107</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>1104.115808</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>502.955247</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>502.925275</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>599.022135</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>390.343117</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>447.129925</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>498.740523</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>428.49604</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>645.801412</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>475.063365</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>509.708086</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>897.667226</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>471.816015</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>800.060856</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>654.171802</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>694.111636</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>625.450391</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>496.615511</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>551.567505</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>698.902934</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>491.808508</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>997.76538</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>603.862733</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>602.103769</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>546.464886</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>613.039766</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>485.893383</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>375.200156</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>549.557927</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>595.253775</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>979.014241</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>607.714124</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>623.506472</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>449.715352</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>501.246284</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>995.186555</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>496.619606</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>449.010747</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>396.353194</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>616.201529</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>803.022593</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>571.481365</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>694.859337</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>495.103975</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>698.792333</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>628.895792</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>591.077774</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>544.507935</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>508.824919</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>893.144481</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>1196.837592</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>592.661021</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>653.336917</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>499.199941</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>589.309181</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>597.499402</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>553.076984</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>406.519828</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>800.900661</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>404.883374</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>389.921204</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>500.071205</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>407.588951</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>598.003417</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>401.522226</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>496.635906</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>355.681238</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>764.229736</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>688.055201</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>498.693381</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>496.675096</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>803.832066</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>606.534204</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>602.842707</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>399.099544</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>529.198625</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>598.531865</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>494.661668</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>496.416552</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>795.513018</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>693.55911</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>498.88314</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>1019.489745</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>698.313029</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>400.707038</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>598.96967</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>499.722244</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>694.027078</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>1066.691828</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>599.907216</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>598.288371</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>502.203939</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>503.3197</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>398.67457</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>495.162871</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>800.645756</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>399.966068</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>593.245785</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>700.916308</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>701.74233</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>597.478197</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>500.751703</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>404.743065</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>409.508126</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>921.626514</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>702.145109</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>595.251783</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>592.420729</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>593.117771</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>695.667978</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>971.153179</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>502.310628</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>693.056061</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>678.123922</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>392.258615</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>406.137882</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>396.092624</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>417.603365</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>804.011181</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>403.637526</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>408.004366</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>599.163038</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>597.925012</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>421.297661</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>682.441834</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>600.048567</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>649.405228</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>767.34832</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>680.371025</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>497.022174</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>494.650732</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>501.135244</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>600.084418</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>783.578275</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>399.132014</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>493.496366</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>554.710711</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>692.021861</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>427.085713</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>500.663411</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>502.225663</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>546.679157</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>675.541505</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>503.50932</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>502.286906</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>417.702935</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>497.362133</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>601.592086</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>596.772071</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>828.577112</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>794.728695</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>502.26768</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>407.25465</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>501.373033</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>994.238599</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>706.164182</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>891.229122</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>900.419469</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>1173.030466</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>796.779392</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>796.924215</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>879.196673</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>700.766158</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>524.733713</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>697.235349</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>548.787968</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>701.555455</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>996.069308</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>702.698425</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>796.490458</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>855.009924</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>793.407224</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>1235.650528</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>908.01058</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>1095.845674</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>596.85635</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>805.807019</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>652.608604</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>798.714061</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="884999943"/>
+        <c:axId val="525169387"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="884999943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="525169387"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="525169387"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="884999943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Entire Pipeline: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$D$1:$D$498</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="498"/>
+                <c:pt idx="0">
+                  <c:v>712.687025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>510.809873</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>888.324321</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>947.701545</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>999.508388</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1155.498305</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1421.835323</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1244.002438</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2191.512485</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2354.901566</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1973.349326</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2398.533346</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2815.797599</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2654.418398</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3126.278475</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3329.409461</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3669.417207</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3465.313183</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3869.66906</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3646.267874</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3708.951127</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4263.404317</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4662.512509</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4537.437508</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4533.667807</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4640.508808</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5146.81704</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5188.55341</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5274.548909</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5423.554583</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5611.05402</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6155.992988</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5760.239119</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5893.499802</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6171.725639</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>6518.507999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6647.929731</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6824.797547</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>6715.119109</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7484.167736</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>7222.49456</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7382.483013</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>7319.576589</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>6776.297255</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>7073.531623</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>6598.202119</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>6861.974611</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6546.304924</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>6661.638118</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>6980.903775</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>6343.755815</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6105.172074</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6703.056413</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6257.824127</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6116.283763</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>6404.323724</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>6137.496738</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>6078.079487</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6180.796404</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>6550.165733</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6081.293548</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6024.58555</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5993.345829</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5856.159997</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>25353.217806</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5709.939323</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5938.847072</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5636.757625</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5557.281733</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5509.162355</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5745.511798</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5715.420747</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5387.267348</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5881.462345</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5848.542008</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5370.75807</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5552.466193</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5857.238516</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5610.827554</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5993.23719</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5739.793469</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5885.686359</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5776.421727</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5972.410352</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5712.538598</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5881.356097</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5514.704563</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5598.273524</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5724.828699</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5675.354562</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5549.216437</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5456.584147</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5726.448156</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5472.270082</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5495.64512</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5127.878897</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5668.02557</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5923.945672</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5648.377111</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5290.130669</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5721.853263</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5718.986799</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5738.979288</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5816.404494</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5385.29669</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5679.342194</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5387.741572</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5306.997579</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5228.160377</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5187.933394</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5084.865635</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5259.245118</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5515.150333</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4869.275795</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5296.711712</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5246.396064</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5333.444993</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>5028.850585</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5421.245045</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5371.325875</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5266.175494</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4992.623165</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5692.15392</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5403.189415</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5127.508425</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5155.108905</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4983.366628</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5194.198406</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5337.383348</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>5458.404994</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4880.266854</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5018.717215</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>5267.560461</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5204.739628</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5000.254541</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>5109.227723</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5146.139604</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5062.207653</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5485.055028</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>5315.523286</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5207.585824</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5095.768517</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>5299.032161</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5144.01301</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>5119.280669</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4952.425848</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>5180.61687</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>5107.478729</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4707.901139</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4960.404946</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>5013.247785</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>4890.420179</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5073.889437</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>5061.737491</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4982.527779</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5275.209744</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4870.972704</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>5042.917051</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>5149.036419</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5291.009376</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5010.328049</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>5234.89003</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>4844.167486</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>4888.822875</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>5252.396144</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>5011.513297</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4790.88049</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4684.483073</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>5012.243352</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4743.934537</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4713.831115</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4450.701181</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4544.954777</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5006.896578</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4958.158437</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4368.149716</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4718.893583</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4586.881566</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4863.233309</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4994.146662</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4451.394348</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4505.697252</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>5101.958547</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4643.772425</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4987.102999</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4427.417507</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4692.47518</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>4305.734878</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5048.025103</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4640.562895</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4554.584298</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4738.812013</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4677.971171</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4569.507113</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4521.896587</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>5022.038735</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>4657.013696</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>4472.402212</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4381.793942</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>4447.722361</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>4696.553306</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>4622.154034</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>4338.270516</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>4352.962497</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>4561.42064</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>4583.943434</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>4196.826795</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>4296.655943</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>4159.32926</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>4249.210134</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>4156.943137</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>4062.743871</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3776.560988</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>4097.538445</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4210.001291</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>3868.216825</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>4099.658798</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>3760.198921</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>3868.397526</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>3830.19485</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>3910.893346</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>3733.616914</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>3669.371142</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>3538.693168</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>3457.638156</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>3440.034316</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>3415.663477</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>3481.233346</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>3469.132548</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>3958.52891</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>3350.404561</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>3440.856079</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>3496.042023</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>3210.471906</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>3853.743512</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>3405.74692</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>3444.164771</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>3735.198539</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>3392.646026</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>3586.976304</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>3642.506851</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>4108.985159</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>3648.961237</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>3464.660984</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>3400.943135</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>3546.831871</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>3640.705523</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>3715.627552</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3439.793647</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>3868.279695</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>3607.486754</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>3904.962447</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>3347.573495</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>3409.743562</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>3623.444198</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>3374.594277</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>3591.966896</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>3587.479758</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>4200.140806</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>3502.349237</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>3544.546249</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>3539.542384</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>3581.541894</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>4273.735975</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>3827.341497</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>3694.618748</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>3800.131055</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>4265.525395</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>4224.753449</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>4042.988392</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>3696.437333</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>3961.934293</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>3915.001762</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>4175.865752</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>4094.610955</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>3814.79369</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>3757.865108</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>3723.833423</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>4298.913436</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>3915.940322</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>3780.819829</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>3873.680127</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>3968.162992</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>3996.247955</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>4005.06122</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4050.035132</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4078.070548</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>3907.245022</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>4143.951352</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>4157.881509</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>4451.866497</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>4364.053374</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4125.790099</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4059.920333</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4405.081704</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4459.988699</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4073.45282</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>3938.911023</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>3923.198608</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>4378.28352</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>4243.294526</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>4045.414245</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>3881.314811</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>3883.395238</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>3983.262287</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>3942.072463</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4139.838573</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>4186.949343</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>3863.976434</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>4085.441153</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>3851.34139</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4187.499413</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>4261.828673</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>4015.478729</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>3881.876344</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>3939.186004</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>4159.752217</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>4168.069976</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>4082.727462</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>4407.186387</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>3899.789641</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>4096.728305</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>4239.331221</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>3674.544424</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>3888.995355</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>3794.516783</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>3851.995961</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>4151.56266</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>3991.099933</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>3889.199028</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>4280.644491</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>3830.884326</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>4318.549084</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>4193.777474</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>3871.874906</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>3887.705366</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>4083.017771</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>4207.610277</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4230.885424</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>3913.086058</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>4405.008886</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>3984.083125</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4144.085722</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>4108.182528</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>4202.457593</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>4231.375127</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>4017.63613</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>4132.051232</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>4144.505883</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>4678.204762</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>4289.742634</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>4051.341912</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>4049.747983</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>4130.095081</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>4749.750383</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4149.747168</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>4019.505224</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>3914.341315</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>4157.140283</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>4548.311203</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>4227.052966</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>4273.318208</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>4151.852307</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>4400.440439</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>4437.108438</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>4409.315958</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>4023.731497</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>3894.315501</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>4600.765151</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>4887.7403</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>4347.135047</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4210.373506</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>3934.865313</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>4409.477747</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>4398.06803</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>4243.847744</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>3942.887975</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>4642.248933</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>4215.232743</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>4112.961597</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>4164.752809</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4129.980433</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4270.051106</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4020.865168</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>4029.733937</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>3983.916463</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4384.882421</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4239.040148</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4217.576116</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>3975.895244</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>4275.166852</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4397.719634</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>4189.786902</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>3917.319923</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>3856.481969</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4152.391904</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4040.382239</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4139.994029</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4137.623486</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>3976.234427</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4041.576381</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4652.548003</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4279.707583</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>3774.582766</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>3976.660624</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>3816.759324</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>4247.416571</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4369.404908</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>4007.758858</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4044.001384</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>3941.972643</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4172.621275</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>3983.035257</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4091.566603</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>4314.282066</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4070.787415</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>4178.364511</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>4256.718841</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4253.310329</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4257.833291</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4273.295534</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>3957.06018</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>3987.304605</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4677.105262</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>4457.198136</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>4066.514079</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>4140.625826</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4023.487083</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4560.301692</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4893.459672</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4165.708843</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4356.455407</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4352.683623</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4287.551172</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4156.40471</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4267.080893</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>4106.870435</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4476.43686</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>3934.212603</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>3980.504835</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4217.149021</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>4054.698134</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>3778.293022</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4067.785934</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4260.31977</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4072.268216</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4194.80896</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4053.746374</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4072.84229</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4084.573919</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4115.753146</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4180.73212</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4228.416056</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>3815.441495</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>4008.40764</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4176.558524</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4287.473256</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4061.296713</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>3855.978802</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>3816.716714</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>3959.489955</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4088.597354</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>3942.086518</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>3748.932396</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>3569.31448</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>3718.945185</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>3878.007485</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>3873.970162</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>4144.170851</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>4045.524664</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>3867.55055</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>4019.793894</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>4060.697604</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>4542.888157</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>4080.111737</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>4314.332763</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>4518.067982</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>4659.439324</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>4450.299005</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>4515.034716</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>4485.396912</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>4483.333994</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>4451.485516</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>4672.547933</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>4565.865261</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>4742.230535</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>4936.447959</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>4617.680747</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>4787.840968</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>4868.854941</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>4922.360758</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>5455.948153</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5261.177884</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>5367.119528</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>4940.708539</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5211.582493</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5361.632554</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>5451.431052</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="958098945"/>
+        <c:axId val="897765176"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="958098945"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="897765176"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="897765176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="958098945"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="2500"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>234315</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3479800" y="63500"/>
+        <a:ext cx="7651115" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3479800" y="2571750"/>
+        <a:ext cx="7658100" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>311150</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3454400" y="5588000"/>
+        <a:ext cx="7753350" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>291465</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3498850" y="8401050"/>
+        <a:ext cx="7689215" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8470,5 +17864,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>